--- a/downld02.xlsx
+++ b/downld02.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH75"/>
+  <dimension ref="A1:AH77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9768,6 +9768,258 @@
         <v>30</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>10/09/26</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>NNE</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>NNE</t>
+        </is>
+      </c>
+      <c r="M76" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="N76" s="4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="O76" s="4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q76" s="4" t="n">
+        <v>1006.3</v>
+      </c>
+      <c r="R76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U76" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V76" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W76" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X76" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y76" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="4" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="AB76" s="4" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AC76" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="AD76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF76" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG76" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH76" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>10/09/26</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K77" s="7" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>ENE</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="N77" s="7" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="O77" s="7" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q77" s="7" t="n">
+        <v>1005.2</v>
+      </c>
+      <c r="R77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U77" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V77" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W77" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X77" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y77" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB77" s="7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AC77" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="AD77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF77" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG77" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH77" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AH1"/>

--- a/downld02.xlsx
+++ b/downld02.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH77"/>
+  <dimension ref="A1:AH78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10020,6 +10020,132 @@
         <v>30</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>10/09/26</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>ENE</t>
+        </is>
+      </c>
+      <c r="M78" s="4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="N78" s="4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="O78" s="4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q78" s="4" t="n">
+        <v>1004.1</v>
+      </c>
+      <c r="R78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U78" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V78" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W78" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X78" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y78" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="4" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="AB78" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AC78" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF78" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG78" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH78" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AH1"/>

--- a/downld02.xlsx
+++ b/downld02.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH78"/>
+  <dimension ref="A1:AH80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10146,6 +10146,258 @@
         <v>30</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>10/09/26</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H79" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K79" s="7" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="M79" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="N79" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="O79" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q79" s="7" t="n">
+        <v>1003.1</v>
+      </c>
+      <c r="R79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U79" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V79" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W79" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X79" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y79" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="7" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AB79" s="7" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AC79" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF79" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG79" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH79" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>10/09/26</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K80" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="M80" s="4" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="N80" s="4" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="O80" s="4" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="n">
+        <v>1002.5</v>
+      </c>
+      <c r="R80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U80" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V80" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W80" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X80" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y80" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="4" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="AB80" s="4" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AC80" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="AD80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF80" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG80" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH80" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AH1"/>

--- a/downld02.xlsx
+++ b/downld02.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH80"/>
+  <dimension ref="A1:AH69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -699,7 +699,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -708,47 +708,47 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>11.7</v>
+        <v>16.7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>11.7</v>
+        <v>18.4</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>11.6</v>
+        <v>16.7</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>NNW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>NNW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="M4" s="4" t="n">
-        <v>11.7</v>
+        <v>16.7</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>1011.5</v>
+        <v>1009.4</v>
       </c>
       <c r="R4" s="4" t="n">
         <v>0</v>
@@ -795,22 +795,22 @@
         </is>
       </c>
       <c r="Z4" s="4" t="n">
-        <v>0.139</v>
+        <v>0.034</v>
       </c>
       <c r="AA4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>21.2</v>
+        <v>23.1</v>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AD4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" s="5" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF4" s="5" t="n">
         <v>5</v>
@@ -825,7 +825,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -834,47 +834,47 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>11.3</v>
+        <v>15.7</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>11.7</v>
+        <v>16.7</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>11.3</v>
+        <v>15.7</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>8.199999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="J5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="M5" s="7" t="n">
-        <v>11.3</v>
+        <v>15.7</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>11.2</v>
+        <v>15.4</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>11.2</v>
+        <v>15.4</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>1011.5</v>
+        <v>1009.8</v>
       </c>
       <c r="R5" s="7" t="n">
         <v>0</v>
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="Z5" s="7" t="n">
-        <v>0.146</v>
+        <v>0.056</v>
       </c>
       <c r="AA5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB5" s="7" t="n">
-        <v>21.2</v>
+        <v>23.1</v>
       </c>
       <c r="AC5" s="8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AD5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AE5" s="8" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF5" s="8" t="n">
         <v>5</v>
@@ -951,7 +951,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -960,47 +960,47 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.9</v>
+        <v>15.7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.3</v>
+        <v>15.7</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.9</v>
+        <v>15.6</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.1</v>
+        <v>11.6</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>WNW</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>WNW</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.9</v>
+        <v>15.7</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.8</v>
+        <v>15.4</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.8</v>
+        <v>15.4</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1011.2</v>
+        <v>1009.4</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>0</v>
@@ -1047,22 +1047,22 @@
         </is>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.155</v>
+        <v>0.056</v>
       </c>
       <c r="AA6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>21.1</v>
+        <v>23.1</v>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AD6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AE6" s="5" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF6" s="5" t="n">
         <v>5</v>
@@ -1077,7 +1077,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -1086,19 +1086,19 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>10.6</v>
+        <v>15.1</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>10.9</v>
+        <v>15.7</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>10.6</v>
+        <v>15.1</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="M7" s="7" t="n">
-        <v>10.6</v>
+        <v>15.1</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>10.6</v>
+        <v>14.9</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>10.6</v>
+        <v>14.9</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>1010.9</v>
+        <v>1009.1</v>
       </c>
       <c r="R7" s="7" t="n">
         <v>0</v>
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="Z7" s="7" t="n">
-        <v>0.161</v>
+        <v>0.067</v>
       </c>
       <c r="AA7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" s="7" t="n">
-        <v>21.1</v>
+        <v>23.1</v>
       </c>
       <c r="AC7" s="8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" s="8" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AF7" s="8" t="n">
         <v>5</v>
@@ -1203,7 +1203,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1212,47 +1212,47 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>14.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10.6</v>
+        <v>15.1</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10</v>
+        <v>14.2</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.6</v>
+        <v>11.1</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="M8" s="4" t="n">
-        <v>10</v>
+        <v>14.2</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>10.1</v>
+        <v>14.1</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.1</v>
+        <v>14.1</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1010.6</v>
+        <v>1009</v>
       </c>
       <c r="R8" s="4" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.174</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AA8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>21.1</v>
+        <v>23.1</v>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD8" s="4" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1338,47 +1338,47 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>9.5</v>
+        <v>14.1</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>10.1</v>
+        <v>14.2</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>9.5</v>
+        <v>13.9</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>7.1</v>
+        <v>11.2</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="J9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="M9" s="7" t="n">
-        <v>9.5</v>
+        <v>14.1</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>9.6</v>
+        <v>13.9</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>9.6</v>
+        <v>13.9</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>1010.3</v>
+        <v>1008.9</v>
       </c>
       <c r="R9" s="7" t="n">
         <v>0</v>
@@ -1425,16 +1425,16 @@
         </is>
       </c>
       <c r="Z9" s="7" t="n">
-        <v>0.184</v>
+        <v>0.089</v>
       </c>
       <c r="AA9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>21</v>
+        <v>23.1</v>
       </c>
       <c r="AC9" s="8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD9" s="7" t="n">
         <v>0</v>
@@ -1455,7 +1455,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1464,47 +1464,47 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8.9</v>
+        <v>14.1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.5</v>
+        <v>14.1</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>8.9</v>
+        <v>14</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.9</v>
+        <v>11.2</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="M10" s="4" t="n">
-        <v>8.9</v>
+        <v>14.1</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>9</v>
+        <v>13.9</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>9</v>
+        <v>13.9</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1010</v>
+        <v>1008.8</v>
       </c>
       <c r="R10" s="4" t="n">
         <v>0</v>
@@ -1551,16 +1551,16 @@
         </is>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.196</v>
+        <v>0.089</v>
       </c>
       <c r="AA10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>20.9</v>
+        <v>23</v>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD10" s="4" t="n">
         <v>0</v>
@@ -1581,7 +1581,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -1590,47 +1590,47 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>8.9</v>
+        <v>14.1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>8.5</v>
+        <v>14</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>6.7</v>
+        <v>11.2</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="J11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>WNW</t>
         </is>
       </c>
       <c r="M11" s="7" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>8.6</v>
+        <v>13.9</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>8.6</v>
+        <v>13.9</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>1009.9</v>
+        <v>1008.3</v>
       </c>
       <c r="R11" s="7" t="n">
         <v>0</v>
@@ -1677,16 +1677,16 @@
         </is>
       </c>
       <c r="Z11" s="7" t="n">
-        <v>0.204</v>
+        <v>0.09</v>
       </c>
       <c r="AA11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="AC11" s="8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD11" s="7" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1716,47 +1716,47 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6.3</v>
+        <v>11.3</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="J12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="M12" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1009.7</v>
+        <v>1008.1</v>
       </c>
       <c r="R12" s="4" t="n">
         <v>0</v>
@@ -1803,16 +1803,16 @@
         </is>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.212</v>
+        <v>0.091</v>
       </c>
       <c r="AA12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD12" s="4" t="n">
         <v>0</v>
@@ -1833,7 +1833,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -1842,47 +1842,47 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>7.8</v>
+        <v>14.6</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>8.199999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7.8</v>
+        <v>13.9</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>6.3</v>
+        <v>11.7</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="J13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="M13" s="7" t="n">
-        <v>7.8</v>
+        <v>14.6</v>
       </c>
       <c r="N13" s="7" t="n">
-        <v>7.9</v>
+        <v>14.4</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>7.9</v>
+        <v>14.4</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>1009.6</v>
+        <v>1007.9</v>
       </c>
       <c r="R13" s="7" t="n">
         <v>0</v>
@@ -1929,16 +1929,16 @@
         </is>
       </c>
       <c r="Z13" s="7" t="n">
-        <v>0.219</v>
+        <v>0.079</v>
       </c>
       <c r="AA13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB13" s="7" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="AC13" s="8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD13" s="7" t="n">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1968,47 +1968,47 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7.5</v>
+        <v>15.1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>7.8</v>
+        <v>15.1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.3</v>
+        <v>14.6</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6</v>
+        <v>11.9</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>WNW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="J14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>WNW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="M14" s="4" t="n">
-        <v>7.5</v>
+        <v>15.1</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1009.5</v>
+        <v>1007.8</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>0</v>
@@ -2055,16 +2055,16 @@
         </is>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.226</v>
+        <v>0.067</v>
       </c>
       <c r="AA14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>20.7</v>
+        <v>22.8</v>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD14" s="4" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -2094,47 +2094,47 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>7.7</v>
+        <v>16.4</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>7.7</v>
+        <v>16.4</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>7.5</v>
+        <v>15.1</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.3</v>
+        <v>12.6</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>WNW</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="J15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>WNW</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
-        <v>7.7</v>
+        <v>16.4</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>7.8</v>
+        <v>16.4</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>7.8</v>
+        <v>16.4</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>1009.3</v>
+        <v>1008.2</v>
       </c>
       <c r="R15" s="7" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
         </is>
       </c>
       <c r="Z15" s="7" t="n">
-        <v>0.221</v>
+        <v>0.039</v>
       </c>
       <c r="AA15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>20.7</v>
+        <v>22.8</v>
       </c>
       <c r="AC15" s="8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AE15" s="8" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF15" s="8" t="n">
         <v>5</v>
@@ -2211,7 +2211,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2220,47 +2220,47 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>8</v>
+        <v>15.3</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>8.1</v>
+        <v>16.6</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.7</v>
+        <v>15.3</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="J16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="M16" s="4" t="n">
-        <v>8</v>
+        <v>15.3</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>8.1</v>
+        <v>15.2</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>8.1</v>
+        <v>15.2</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1009.3</v>
+        <v>1008.2</v>
       </c>
       <c r="R16" s="4" t="n">
         <v>0</v>
@@ -2307,16 +2307,16 @@
         </is>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.215</v>
+        <v>0.064</v>
       </c>
       <c r="AA16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>20.6</v>
+        <v>22.8</v>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD16" s="4" t="n">
         <v>0</v>
@@ -2337,7 +2337,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -2346,47 +2346,47 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>7.8</v>
+        <v>14.7</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>8</v>
+        <v>15.3</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>7.8</v>
+        <v>14.7</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>6.2</v>
+        <v>11.6</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="J17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="M17" s="7" t="n">
-        <v>7.8</v>
+        <v>14.7</v>
       </c>
       <c r="N17" s="7" t="n">
-        <v>7.8</v>
+        <v>14.6</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>7.8</v>
+        <v>14.6</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>1009.5</v>
+        <v>1008.3</v>
       </c>
       <c r="R17" s="7" t="n">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="Z17" s="7" t="n">
-        <v>0.22</v>
+        <v>0.076</v>
       </c>
       <c r="AA17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB17" s="7" t="n">
-        <v>20.6</v>
+        <v>22.7</v>
       </c>
       <c r="AC17" s="8" t="n">
         <v>53</v>
@@ -2448,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="AE17" s="8" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF17" s="8" t="n">
         <v>5</v>
@@ -2463,7 +2463,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2472,19 +2472,19 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>7.8</v>
+        <v>15.4</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>7.7</v>
+        <v>14.6</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>6.3</v>
+        <v>12.4</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>0</v>
@@ -2506,13 +2506,13 @@
         </is>
       </c>
       <c r="M18" s="4" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1009.9</v>
+        <v>1008.6</v>
       </c>
       <c r="R18" s="4" t="n">
         <v>0</v>
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.222</v>
+        <v>0.06</v>
       </c>
       <c r="AA18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>20.5</v>
+        <v>22.7</v>
       </c>
       <c r="AC18" s="5" t="n">
         <v>53</v>
@@ -2589,7 +2589,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -2598,47 +2598,47 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>8.199999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>8.199999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>6.8</v>
+        <v>13.1</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>WNW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="J19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>WNW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="M19" s="7" t="n">
-        <v>8.199999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="N19" s="7" t="n">
-        <v>8.300000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>8.300000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>1010.1</v>
+        <v>1009</v>
       </c>
       <c r="R19" s="7" t="n">
         <v>0</v>
@@ -2685,16 +2685,16 @@
         </is>
       </c>
       <c r="Z19" s="7" t="n">
-        <v>0.211</v>
+        <v>0.034</v>
       </c>
       <c r="AA19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB19" s="7" t="n">
-        <v>20.4</v>
+        <v>22.6</v>
       </c>
       <c r="AC19" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AD19" s="7" t="n">
         <v>0</v>
@@ -2715,7 +2715,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2724,19 +2724,19 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>10.6</v>
+        <v>17.6</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>10.6</v>
+        <v>17.6</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>9.1</v>
+        <v>13.7</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>0</v>
@@ -2758,13 +2758,13 @@
         </is>
       </c>
       <c r="M20" s="4" t="n">
-        <v>10.6</v>
+        <v>17.6</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>10.7</v>
+        <v>17.6</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>10.7</v>
+        <v>17.6</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1010.3</v>
+        <v>1009.3</v>
       </c>
       <c r="R20" s="4" t="n">
         <v>0</v>
@@ -2811,16 +2811,16 @@
         </is>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.162</v>
+        <v>0.016</v>
       </c>
       <c r="AA20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>20.3</v>
+        <v>22.8</v>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AD20" s="4" t="n">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -2850,47 +2850,47 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>13.8</v>
+        <v>18.9</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>13.8</v>
+        <v>18.9</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>10.6</v>
+        <v>17.6</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>9.9</v>
+        <v>13.9</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="J21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
-        <v>13.8</v>
+        <v>18.9</v>
       </c>
       <c r="N21" s="7" t="n">
-        <v>13.6</v>
+        <v>18.9</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>13.6</v>
+        <v>18.9</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>1010.1</v>
+        <v>1009.2</v>
       </c>
       <c r="R21" s="7" t="n">
         <v>0</v>
@@ -2937,22 +2937,22 @@
         </is>
       </c>
       <c r="Z21" s="7" t="n">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="7" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="AB21" s="7" t="n">
-        <v>20.3</v>
+        <v>22.9</v>
       </c>
       <c r="AC21" s="8" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AD21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AE21" s="8" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF21" s="8" t="n">
         <v>5</v>
@@ -2967,7 +2967,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2976,47 +2976,47 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>16.6</v>
+        <v>19.8</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>16.6</v>
+        <v>19.8</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>13.9</v>
+        <v>18.9</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>10.6</v>
+        <v>14.4</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="J22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="M22" s="4" t="n">
-        <v>16.6</v>
+        <v>19.8</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>16.1</v>
+        <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>16.1</v>
+        <v>20</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1009.7</v>
+        <v>1009</v>
       </c>
       <c r="R22" s="4" t="n">
         <v>0</v>
@@ -3063,16 +3063,16 @@
         </is>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>20.3</v>
+        <v>23.1</v>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AD22" s="4" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -3102,26 +3102,26 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>18.6</v>
+        <v>20.8</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>18.6</v>
+        <v>20.8</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>16.5</v>
+        <v>19.8</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>11.1</v>
+        <v>14.9</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="J23" s="7" t="n">
@@ -3132,17 +3132,17 @@
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>WSW</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="M23" s="7" t="n">
-        <v>18.6</v>
+        <v>20.8</v>
       </c>
       <c r="N23" s="7" t="n">
-        <v>18.1</v>
+        <v>20.9</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>18.1</v>
+        <v>20.9</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>1009.4</v>
+        <v>1008.9</v>
       </c>
       <c r="R23" s="7" t="n">
         <v>0</v>
@@ -3192,13 +3192,13 @@
         <v>0</v>
       </c>
       <c r="AA23" s="7" t="n">
-        <v>0.005</v>
+        <v>0.051</v>
       </c>
       <c r="AB23" s="7" t="n">
-        <v>20.4</v>
+        <v>23</v>
       </c>
       <c r="AC23" s="8" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AD23" s="7" t="n">
         <v>0</v>
@@ -3219,7 +3219,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3228,47 +3228,47 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>18.6</v>
+        <v>20.7</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>10.4</v>
+        <v>14.8</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>WSW</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="J24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="M24" s="4" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1009</v>
+        <v>1008.7</v>
       </c>
       <c r="R24" s="4" t="n">
         <v>0</v>
@@ -3318,19 +3318,19 @@
         <v>0</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>20.7</v>
+        <v>23.1</v>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AD24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AE24" s="5" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF24" s="5" t="n">
         <v>5</v>
@@ -3345,7 +3345,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -3354,47 +3354,47 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>10</v>
+        <v>14.9</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>WSW</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="M25" s="7" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="N25" s="7" t="n">
-        <v>22.4</v>
+        <v>23.5</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>22.4</v>
+        <v>23.5</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>1008.4</v>
+        <v>1008.5</v>
       </c>
       <c r="R25" s="7" t="n">
         <v>0</v>
@@ -3444,13 +3444,13 @@
         <v>0</v>
       </c>
       <c r="AA25" s="7" t="n">
-        <v>0.096</v>
+        <v>0.104</v>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>20.7</v>
+        <v>23.1</v>
       </c>
       <c r="AC25" s="8" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AD25" s="7" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -3486,41 +3486,41 @@
         <v>24.9</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="M26" s="4" t="n">
         <v>24.9</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>24.4</v>
+        <v>24.9</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>24.4</v>
+        <v>24.9</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1007.7</v>
+        <v>1008.1</v>
       </c>
       <c r="R26" s="4" t="n">
         <v>0</v>
@@ -3570,19 +3570,19 @@
         <v>0</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>20.7</v>
+        <v>23.2</v>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AD26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AE26" s="5" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF26" s="5" t="n">
         <v>5</v>
@@ -3597,7 +3597,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -3606,47 +3606,47 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>26.2</v>
+        <v>27.1</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>24.9</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>10.7</v>
+        <v>16.1</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>ESE</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="J27" s="7" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K27" s="7" t="n">
         <v>8</v>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="M27" s="7" t="n">
-        <v>26.2</v>
+        <v>27.1</v>
       </c>
       <c r="N27" s="7" t="n">
-        <v>25.4</v>
+        <v>27.3</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>25.4</v>
+        <v>27.3</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>1007.1</v>
+        <v>1007.2</v>
       </c>
       <c r="R27" s="7" t="n">
         <v>0</v>
@@ -3696,19 +3696,19 @@
         <v>0</v>
       </c>
       <c r="AA27" s="7" t="n">
-        <v>0.163</v>
+        <v>0.182</v>
       </c>
       <c r="AB27" s="7" t="n">
-        <v>20.8</v>
+        <v>23.2</v>
       </c>
       <c r="AC27" s="8" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AD27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AE27" s="8" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF27" s="8" t="n">
         <v>5</v>
@@ -3723,7 +3723,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3732,47 +3732,47 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>27.6</v>
+        <v>27.2</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>27.6</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>25.9</v>
+        <v>27</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>12</v>
+        <v>15.8</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.8</v>
+        <v>1.61</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>27.6</v>
+        <v>27.2</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>26.8</v>
+        <v>27.3</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>26.8</v>
+        <v>27.3</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1006.2</v>
+        <v>1006.3</v>
       </c>
       <c r="R28" s="4" t="n">
         <v>0</v>
@@ -3822,13 +3822,13 @@
         <v>0</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>0.192</v>
+        <v>0.184</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>20.8</v>
+        <v>23.3</v>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AD28" s="4" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -3858,47 +3858,47 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>29.1</v>
+        <v>27.9</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>29.1</v>
+        <v>27.9</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G29" s="7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K29" s="7" t="n">
         <v>12.9</v>
       </c>
-      <c r="H29" s="7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>ESE</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>16.1</v>
-      </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>ENE</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
-        <v>29.1</v>
+        <v>27.9</v>
       </c>
       <c r="N29" s="7" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>1005.4</v>
+        <v>1005.2</v>
       </c>
       <c r="R29" s="7" t="n">
         <v>0</v>
@@ -3948,13 +3948,13 @@
         <v>0</v>
       </c>
       <c r="AA29" s="7" t="n">
-        <v>0.225</v>
+        <v>0.2</v>
       </c>
       <c r="AB29" s="7" t="n">
-        <v>20.9</v>
+        <v>23.4</v>
       </c>
       <c r="AC29" s="8" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AD29" s="7" t="n">
         <v>0</v>
@@ -3975,7 +3975,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3984,22 +3984,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>29.8</v>
+        <v>27.3</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>29.9</v>
+        <v>28.1</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>29.1</v>
+        <v>27.2</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
@@ -4007,24 +4007,24 @@
         </is>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.41</v>
+        <v>1.61</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>16.1</v>
+        <v>11.3</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>ENE</t>
         </is>
       </c>
       <c r="M30" s="4" t="n">
-        <v>29.8</v>
+        <v>27.3</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>29.1</v>
+        <v>27.3</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>29.1</v>
+        <v>27.3</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1004.3</v>
+        <v>1004.1</v>
       </c>
       <c r="R30" s="4" t="n">
         <v>0</v>
@@ -4074,19 +4074,19 @@
         <v>0</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>0.24</v>
+        <v>0.186</v>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>21.1</v>
+        <v>23.6</v>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="AD30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AE30" s="5" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AF30" s="5" t="n">
         <v>5</v>
@@ -4101,7 +4101,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -4110,47 +4110,47 @@
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>30.5</v>
+        <v>29</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>30.5</v>
+        <v>29</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>29.8</v>
+        <v>27.3</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>13.3</v>
+        <v>15.5</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>ENE</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="J31" s="7" t="n">
-        <v>2.41</v>
+        <v>0.8</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>17.7</v>
+        <v>11.3</v>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>ENE</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="M31" s="7" t="n">
-        <v>30.5</v>
+        <v>29</v>
       </c>
       <c r="N31" s="7" t="n">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>1003.8</v>
+        <v>1003.1</v>
       </c>
       <c r="R31" s="7" t="n">
         <v>0</v>
@@ -4200,13 +4200,13 @@
         <v>0</v>
       </c>
       <c r="AA31" s="7" t="n">
-        <v>0.253</v>
+        <v>0.222</v>
       </c>
       <c r="AB31" s="7" t="n">
-        <v>21.2</v>
+        <v>23.8</v>
       </c>
       <c r="AC31" s="8" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="AD31" s="7" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -4236,22 +4236,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>30.4</v>
+        <v>29.2</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>30.6</v>
+        <v>29.7</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>30.3</v>
+        <v>29</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>13.3</v>
+        <v>16.4</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.22</v>
+        <v>1.61</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>16.1</v>
+        <v>14.5</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
@@ -4270,13 +4270,13 @@
         </is>
       </c>
       <c r="M32" s="4" t="n">
-        <v>30.4</v>
+        <v>29.2</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>1003.2</v>
+        <v>1002.5</v>
       </c>
       <c r="R32" s="4" t="n">
         <v>0</v>
@@ -4326,13 +4326,13 @@
         <v>0</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>0.252</v>
+        <v>0.226</v>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>21.3</v>
+        <v>23.9</v>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="AD32" s="4" t="n">
         <v>0</v>
@@ -4353,7 +4353,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -4362,47 +4362,47 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>30.8</v>
+        <v>28.2</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>31.2</v>
+        <v>29.2</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>30.4</v>
+        <v>28.2</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>13.1</v>
+        <v>15.8</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>ENE</t>
+          <t>ESE</t>
         </is>
       </c>
       <c r="J33" s="7" t="n">
-        <v>2.41</v>
+        <v>0.8</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>14.5</v>
+        <v>12.9</v>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>ENE</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="M33" s="7" t="n">
-        <v>30.8</v>
+        <v>28.2</v>
       </c>
       <c r="N33" s="7" t="n">
-        <v>30</v>
+        <v>28.3</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>30</v>
+        <v>28.3</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="Q33" s="7" t="n">
-        <v>1002.6</v>
+        <v>1002.1</v>
       </c>
       <c r="R33" s="7" t="n">
         <v>0</v>
@@ -4452,19 +4452,19 @@
         <v>0</v>
       </c>
       <c r="AA33" s="7" t="n">
-        <v>0.259</v>
+        <v>0.205</v>
       </c>
       <c r="AB33" s="7" t="n">
-        <v>21.4</v>
+        <v>24.2</v>
       </c>
       <c r="AC33" s="8" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="AD33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AE33" s="8" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AF33" s="8" t="n">
         <v>5</v>
@@ -4479,7 +4479,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4488,47 +4488,47 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>31.5</v>
+        <v>28.7</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>31.5</v>
+        <v>28.7</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>30.7</v>
+        <v>28.1</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>13.3</v>
+        <v>16.3</v>
       </c>
       <c r="H34" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>ENE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="J34" s="4" t="n">
         <v>1.61</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>16.1</v>
+        <v>14.5</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="M34" s="4" t="n">
-        <v>31.5</v>
+        <v>28.7</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>30.7</v>
+        <v>28.9</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>30.7</v>
+        <v>28.9</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1002.3</v>
+        <v>1001.2</v>
       </c>
       <c r="R34" s="4" t="n">
         <v>0</v>
@@ -4578,13 +4578,13 @@
         <v>0</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>0.274</v>
+        <v>0.216</v>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>21.6</v>
+        <v>24.2</v>
       </c>
       <c r="AC34" s="5" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AD34" s="4" t="n">
         <v>0</v>
@@ -4605,7 +4605,7 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -4614,47 +4614,47 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>31.4</v>
+        <v>29.5</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>31.8</v>
+        <v>29.6</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>31.4</v>
+        <v>28.7</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>13.2</v>
+        <v>16.3</v>
       </c>
       <c r="H35" s="7" t="n">
         <v>1.6</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>ENE</t>
+          <t>ESE</t>
         </is>
       </c>
       <c r="J35" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>12.9</v>
+        <v>11.3</v>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>ESE</t>
         </is>
       </c>
       <c r="M35" s="7" t="n">
-        <v>31.4</v>
+        <v>29.5</v>
       </c>
       <c r="N35" s="7" t="n">
-        <v>30.7</v>
+        <v>29.7</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>30.7</v>
+        <v>29.7</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="Q35" s="7" t="n">
-        <v>1001.9</v>
+        <v>1000.8</v>
       </c>
       <c r="R35" s="7" t="n">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0</v>
       </c>
       <c r="AA35" s="7" t="n">
-        <v>0.273</v>
+        <v>0.233</v>
       </c>
       <c r="AB35" s="7" t="n">
-        <v>21.8</v>
+        <v>24.2</v>
       </c>
       <c r="AC35" s="8" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AD35" s="7" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -4740,26 +4740,26 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>30.9</v>
+        <v>29.1</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>31.5</v>
+        <v>29.5</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>30.9</v>
+        <v>28.9</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>12.8</v>
+        <v>16.9</v>
       </c>
       <c r="H36" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>ESE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="J36" s="4" t="n">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>ESE</t>
         </is>
       </c>
       <c r="M36" s="4" t="n">
-        <v>30.9</v>
+        <v>29.1</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>30.1</v>
+        <v>29.6</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>30.1</v>
+        <v>29.6</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>1001.8</v>
+        <v>1000.3</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>0</v>
@@ -4830,22 +4830,22 @@
         <v>0</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>0.263</v>
+        <v>0.223</v>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>21.9</v>
+        <v>24.3</v>
       </c>
       <c r="AC36" s="5" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AD36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AE36" s="5" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF36" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG36" s="4" t="n">
         <v>100</v>
@@ -4857,7 +4857,7 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -4866,19 +4866,19 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>30.4</v>
+        <v>28.6</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>31</v>
+        <v>29.1</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>30.4</v>
+        <v>28.6</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>12.8</v>
+        <v>16.8</v>
       </c>
       <c r="H37" s="7" t="n">
         <v>1.6</v>
@@ -4892,21 +4892,21 @@
         <v>0.8</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>11.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="M37" s="7" t="n">
-        <v>30.4</v>
+        <v>28.6</v>
       </c>
       <c r="N37" s="7" t="n">
-        <v>29.6</v>
+        <v>29.1</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>29.6</v>
+        <v>29.1</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="Q37" s="7" t="n">
-        <v>1002.3</v>
+        <v>1000.3</v>
       </c>
       <c r="R37" s="7" t="n">
         <v>0</v>
@@ -4956,13 +4956,13 @@
         <v>0</v>
       </c>
       <c r="AA37" s="7" t="n">
-        <v>0.252</v>
+        <v>0.214</v>
       </c>
       <c r="AB37" s="7" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="AC37" s="8" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AD37" s="7" t="n">
         <v>0</v>
@@ -4983,7 +4983,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -4992,19 +4992,19 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>30</v>
+        <v>28.3</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>30.4</v>
+        <v>28.6</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>29.9</v>
+        <v>28.2</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>12.4</v>
+        <v>17.2</v>
       </c>
       <c r="H38" s="4" t="n">
         <v>1.6</v>
@@ -5018,21 +5018,21 @@
         <v>0.8</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>ENE</t>
+          <t>ESE</t>
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>30</v>
+        <v>28.3</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>29.1</v>
+        <v>28.8</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>29.1</v>
+        <v>28.8</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>1002.7</v>
+        <v>1000.1</v>
       </c>
       <c r="R38" s="4" t="n">
         <v>0</v>
@@ -5082,13 +5082,13 @@
         <v>0</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>0.243</v>
+        <v>0.207</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>22.2</v>
+        <v>24.3</v>
       </c>
       <c r="AC38" s="5" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -5109,7 +5109,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -5118,22 +5118,22 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>29.9</v>
+        <v>27.8</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>30</v>
+        <v>28.3</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>29.9</v>
+        <v>27.8</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>13.2</v>
+        <v>17</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="J39" s="7" t="n">
-        <v>0.8</v>
+        <v>1.61</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>8</v>
+        <v>12.9</v>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
@@ -5152,13 +5152,13 @@
         </is>
       </c>
       <c r="M39" s="7" t="n">
-        <v>29.9</v>
+        <v>27.8</v>
       </c>
       <c r="N39" s="7" t="n">
-        <v>29.2</v>
+        <v>28.3</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>29.2</v>
+        <v>28.3</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="Q39" s="7" t="n">
-        <v>1003.3</v>
+        <v>1000</v>
       </c>
       <c r="R39" s="7" t="n">
         <v>0</v>
@@ -5208,13 +5208,13 @@
         <v>0</v>
       </c>
       <c r="AA39" s="7" t="n">
-        <v>0.242</v>
+        <v>0.197</v>
       </c>
       <c r="AB39" s="7" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="AC39" s="8" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AD39" s="7" t="n">
         <v>0</v>
@@ -5235,7 +5235,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -5244,22 +5244,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>28.9</v>
+        <v>27.1</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>29.9</v>
+        <v>27.8</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>28.9</v>
+        <v>27.1</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0.8</v>
+        <v>1.61</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>9.699999999999999</v>
@@ -5278,13 +5278,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>28.9</v>
+        <v>27.1</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>28.4</v>
+        <v>27.6</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>28.4</v>
+        <v>27.6</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>1003.9</v>
+        <v>999.9</v>
       </c>
       <c r="R40" s="4" t="n">
         <v>0</v>
@@ -5334,19 +5334,19 @@
         <v>0</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>0.221</v>
+        <v>0.182</v>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="AC40" s="5" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AD40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AE40" s="5" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AF40" s="5" t="n">
         <v>5</v>
@@ -5361,7 +5361,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -5370,47 +5370,47 @@
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>26.8</v>
+        <v>25.8</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>28.9</v>
+        <v>27.1</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>26.8</v>
+        <v>25.8</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>13.5</v>
+        <v>17.2</v>
       </c>
       <c r="H41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
           <t>ENE</t>
         </is>
       </c>
-      <c r="J41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>ENE</t>
-        </is>
-      </c>
       <c r="M41" s="7" t="n">
-        <v>26.8</v>
+        <v>25.8</v>
       </c>
       <c r="N41" s="7" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="O41" s="7" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="Q41" s="7" t="n">
-        <v>1004.7</v>
+        <v>999.9</v>
       </c>
       <c r="R41" s="7" t="n">
         <v>0</v>
@@ -5460,13 +5460,13 @@
         <v>0</v>
       </c>
       <c r="AA41" s="7" t="n">
-        <v>0.176</v>
+        <v>0.155</v>
       </c>
       <c r="AB41" s="7" t="n">
-        <v>22.6</v>
+        <v>24.4</v>
       </c>
       <c r="AC41" s="8" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AD41" s="7" t="n">
         <v>0</v>
@@ -5487,7 +5487,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -5496,47 +5496,47 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>26.8</v>
+        <v>25.8</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>13.5</v>
+        <v>16.6</v>
       </c>
       <c r="H42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>WNW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="J42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>WNW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>23.3</v>
+        <v>24.2</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>23.3</v>
+        <v>24.2</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>1005.4</v>
+        <v>1000.5</v>
       </c>
       <c r="R42" s="4" t="n">
         <v>0</v>
@@ -5586,13 +5586,13 @@
         <v>0</v>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>0.104</v>
+        <v>0.113</v>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>22.6</v>
+        <v>24.4</v>
       </c>
       <c r="AC42" s="5" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AD42" s="4" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -5622,19 +5622,19 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>23.3</v>
+        <v>23.7</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H43" s="7" t="n">
         <v>0</v>
@@ -5656,13 +5656,13 @@
         </is>
       </c>
       <c r="M43" s="7" t="n">
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
       <c r="N43" s="7" t="n">
-        <v>21.1</v>
+        <v>22.7</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>21.1</v>
+        <v>22.7</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         </is>
       </c>
       <c r="Q43" s="7" t="n">
-        <v>1006.3</v>
+        <v>1000.9</v>
       </c>
       <c r="R43" s="7" t="n">
         <v>0</v>
@@ -5712,13 +5712,13 @@
         <v>0</v>
       </c>
       <c r="AA43" s="7" t="n">
-        <v>0.064</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AB43" s="7" t="n">
-        <v>22.7</v>
+        <v>24.4</v>
       </c>
       <c r="AC43" s="8" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AD43" s="7" t="n">
         <v>0</v>
@@ -5739,7 +5739,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -5748,19 +5748,19 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>13.2</v>
+        <v>15.8</v>
       </c>
       <c r="H44" s="4" t="n">
         <v>0</v>
@@ -5782,13 +5782,13 @@
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>20.6</v>
+        <v>21.2</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>20.6</v>
+        <v>21.2</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>1006.9</v>
+        <v>1001.1</v>
       </c>
       <c r="R44" s="4" t="n">
         <v>0</v>
@@ -5838,13 +5838,13 @@
         <v>0</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>22.7</v>
+        <v>24.4</v>
       </c>
       <c r="AC44" s="5" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AD44" s="4" t="n">
         <v>0</v>
@@ -5865,7 +5865,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -5874,47 +5874,47 @@
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>19.9</v>
+        <v>20.7</v>
       </c>
       <c r="D45" s="7" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>NNW</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>NNW</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="n">
         <v>20.7</v>
       </c>
-      <c r="E45" s="7" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F45" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="G45" s="7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="H45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="n">
-        <v>19.9</v>
-      </c>
       <c r="N45" s="7" t="n">
-        <v>19.9</v>
+        <v>21.1</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>19.9</v>
+        <v>21.1</v>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         </is>
       </c>
       <c r="Q45" s="7" t="n">
-        <v>1007.7</v>
+        <v>1001.4</v>
       </c>
       <c r="R45" s="7" t="n">
         <v>0</v>
@@ -5964,13 +5964,13 @@
         <v>0</v>
       </c>
       <c r="AA45" s="7" t="n">
-        <v>0.034</v>
+        <v>0.05</v>
       </c>
       <c r="AB45" s="7" t="n">
-        <v>22.7</v>
+        <v>24.5</v>
       </c>
       <c r="AC45" s="8" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AD45" s="7" t="n">
         <v>0</v>
@@ -5991,7 +5991,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -6000,26 +6000,26 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>19.1</v>
+        <v>20.8</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>19.9</v>
+        <v>20.8</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>19.1</v>
+        <v>20.7</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>12.8</v>
+        <v>15.6</v>
       </c>
       <c r="H46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="J46" s="4" t="n">
@@ -6034,13 +6034,13 @@
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>19.1</v>
+        <v>20.8</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>19</v>
+        <v>21.2</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>19</v>
+        <v>21.2</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>1008.5</v>
+        <v>1001.9</v>
       </c>
       <c r="R46" s="4" t="n">
         <v>0</v>
@@ -6090,13 +6090,13 @@
         <v>0</v>
       </c>
       <c r="AA46" s="4" t="n">
-        <v>0.016</v>
+        <v>0.052</v>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>22.8</v>
+        <v>24.6</v>
       </c>
       <c r="AC46" s="5" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AD46" s="4" t="n">
         <v>0</v>
@@ -6117,7 +6117,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -6126,26 +6126,26 @@
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>18.4</v>
+        <v>20.7</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>19.1</v>
+        <v>21</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>18.4</v>
+        <v>20.7</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>12.7</v>
+        <v>15.2</v>
       </c>
       <c r="H47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>NNW</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J47" s="7" t="n">
@@ -6156,17 +6156,17 @@
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
-        <v>18.4</v>
+        <v>20.7</v>
       </c>
       <c r="N47" s="7" t="n">
-        <v>18.3</v>
+        <v>20.9</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>18.3</v>
+        <v>20.9</v>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="Q47" s="7" t="n">
-        <v>1008.6</v>
+        <v>1002.2</v>
       </c>
       <c r="R47" s="7" t="n">
         <v>0</v>
@@ -6216,19 +6216,19 @@
         <v>0</v>
       </c>
       <c r="AA47" s="7" t="n">
-        <v>0.002</v>
+        <v>0.049</v>
       </c>
       <c r="AB47" s="7" t="n">
-        <v>22.9</v>
+        <v>24.6</v>
       </c>
       <c r="AC47" s="8" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AD47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AE47" s="8" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF47" s="8" t="n">
         <v>5</v>
@@ -6243,7 +6243,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -6252,47 +6252,47 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>18.1</v>
+        <v>20</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>18.4</v>
+        <v>20.7</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>18.1</v>
+        <v>20</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="H48" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>NNW</t>
+          <t>WNW</t>
         </is>
       </c>
       <c r="J48" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>NNW</t>
+          <t>WNW</t>
         </is>
       </c>
       <c r="M48" s="4" t="n">
-        <v>18.1</v>
+        <v>20</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>17.8</v>
+        <v>20.3</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>17.8</v>
+        <v>20.3</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>1008.6</v>
+        <v>1002.3</v>
       </c>
       <c r="R48" s="4" t="n">
         <v>0</v>
@@ -6339,16 +6339,16 @@
         </is>
       </c>
       <c r="Z48" s="4" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AA48" s="4" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>22.9</v>
+        <v>24.6</v>
       </c>
       <c r="AC48" s="5" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AD48" s="4" t="n">
         <v>0</v>
@@ -6369,7 +6369,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -6378,47 +6378,47 @@
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>17.9</v>
+        <v>18.9</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>12.4</v>
+        <v>14.6</v>
       </c>
       <c r="H49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>NNW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="J49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>---</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="N49" s="7" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         </is>
       </c>
       <c r="Q49" s="7" t="n">
-        <v>1008.6</v>
+        <v>1002.4</v>
       </c>
       <c r="R49" s="7" t="n">
         <v>0</v>
@@ -6465,16 +6465,16 @@
         </is>
       </c>
       <c r="Z49" s="7" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="7" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="AB49" s="7" t="n">
-        <v>23</v>
+        <v>24.6</v>
       </c>
       <c r="AC49" s="8" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AD49" s="7" t="n">
         <v>0</v>
@@ -6495,7 +6495,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>9/09/26</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -6504,41 +6504,41 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>12.4</v>
+        <v>14.3</v>
       </c>
       <c r="H50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="J50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>NNW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="M50" s="4" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>18.2</v>
@@ -6552,7 +6552,7 @@
         </is>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>1008.8</v>
+        <v>1002.4</v>
       </c>
       <c r="R50" s="4" t="n">
         <v>0</v>
@@ -6591,16 +6591,16 @@
         </is>
       </c>
       <c r="Z50" s="4" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AA50" s="4" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AB50" s="4" t="n">
-        <v>23.1</v>
+        <v>24.6</v>
       </c>
       <c r="AC50" s="5" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AD50" s="4" t="n">
         <v>0</v>
@@ -6621,7 +6621,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -6630,26 +6630,26 @@
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>18.2</v>
+        <v>17.3</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>18.2</v>
+        <v>17.3</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>12.2</v>
+        <v>14.2</v>
       </c>
       <c r="H51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>WNW</t>
         </is>
       </c>
       <c r="J51" s="7" t="n">
@@ -6660,17 +6660,17 @@
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>WNW</t>
         </is>
       </c>
       <c r="M51" s="7" t="n">
-        <v>18.2</v>
+        <v>17.3</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="Q51" s="7" t="n">
-        <v>1009.1</v>
+        <v>1002.5</v>
       </c>
       <c r="R51" s="7" t="n">
         <v>0</v>
@@ -6717,16 +6717,16 @@
         </is>
       </c>
       <c r="Z51" s="7" t="n">
-        <v>0.002</v>
+        <v>0.022</v>
       </c>
       <c r="AA51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB51" s="7" t="n">
-        <v>23.1</v>
+        <v>24.6</v>
       </c>
       <c r="AC51" s="8" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AD51" s="7" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -6756,19 +6756,19 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>18.4</v>
+        <v>17.4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>16.7</v>
+        <v>17.2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>11.9</v>
+        <v>14.1</v>
       </c>
       <c r="H52" s="4" t="n">
         <v>0</v>
@@ -6790,13 +6790,13 @@
         </is>
       </c>
       <c r="M52" s="4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         </is>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>1009.4</v>
+        <v>1002.6</v>
       </c>
       <c r="R52" s="4" t="n">
         <v>0</v>
@@ -6843,22 +6843,22 @@
         </is>
       </c>
       <c r="Z52" s="4" t="n">
-        <v>0.034</v>
+        <v>0.019</v>
       </c>
       <c r="AA52" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>23.1</v>
+        <v>24.6</v>
       </c>
       <c r="AC52" s="5" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD52" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AE52" s="5" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AF52" s="5" t="n">
         <v>5</v>
@@ -6873,7 +6873,7 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -6882,47 +6882,47 @@
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>15.7</v>
+        <v>17.3</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>15.7</v>
+        <v>17.3</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>11.4</v>
+        <v>14.2</v>
       </c>
       <c r="H53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="J53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="M53" s="7" t="n">
-        <v>15.7</v>
+        <v>17.3</v>
       </c>
       <c r="N53" s="7" t="n">
-        <v>15.4</v>
+        <v>17.5</v>
       </c>
       <c r="O53" s="7" t="n">
-        <v>15.4</v>
+        <v>17.5</v>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="Q53" s="7" t="n">
-        <v>1009.8</v>
+        <v>1002.5</v>
       </c>
       <c r="R53" s="7" t="n">
         <v>0</v>
@@ -6969,16 +6969,16 @@
         </is>
       </c>
       <c r="Z53" s="7" t="n">
-        <v>0.056</v>
+        <v>0.021</v>
       </c>
       <c r="AA53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB53" s="7" t="n">
-        <v>23.1</v>
+        <v>24.6</v>
       </c>
       <c r="AC53" s="8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD53" s="7" t="n">
         <v>0</v>
@@ -6999,7 +6999,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -7008,47 +7008,47 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>15.7</v>
+        <v>17.3</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>15.7</v>
+        <v>17.4</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>15.6</v>
+        <v>17.2</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>11.6</v>
+        <v>14.2</v>
       </c>
       <c r="H54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="J54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="M54" s="4" t="n">
-        <v>15.7</v>
+        <v>17.3</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>15.4</v>
+        <v>17.5</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>15.4</v>
+        <v>17.5</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>1009.4</v>
+        <v>1002</v>
       </c>
       <c r="R54" s="4" t="n">
         <v>0</v>
@@ -7095,22 +7095,22 @@
         </is>
       </c>
       <c r="Z54" s="4" t="n">
-        <v>0.056</v>
+        <v>0.021</v>
       </c>
       <c r="AA54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>23.1</v>
+        <v>24.5</v>
       </c>
       <c r="AC54" s="5" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AE54" s="5" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AF54" s="5" t="n">
         <v>5</v>
@@ -7125,7 +7125,7 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -7134,47 +7134,47 @@
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>15.1</v>
+        <v>17.5</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>15.7</v>
+        <v>17.7</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>15.1</v>
+        <v>17.3</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>11.5</v>
+        <v>14.2</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="J55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="M55" s="7" t="n">
-        <v>15.1</v>
+        <v>17.5</v>
       </c>
       <c r="N55" s="7" t="n">
-        <v>14.9</v>
+        <v>17.7</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>14.9</v>
+        <v>17.7</v>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="Q55" s="7" t="n">
-        <v>1009.1</v>
+        <v>1002</v>
       </c>
       <c r="R55" s="7" t="n">
         <v>0</v>
@@ -7221,16 +7221,16 @@
         </is>
       </c>
       <c r="Z55" s="7" t="n">
-        <v>0.067</v>
+        <v>0.017</v>
       </c>
       <c r="AA55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB55" s="7" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="AC55" s="8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD55" s="7" t="n">
         <v>0</v>
@@ -7251,7 +7251,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -7260,47 +7260,47 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>14.2</v>
+        <v>17.6</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>15.1</v>
+        <v>17.6</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>14.2</v>
+        <v>17.4</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>11.1</v>
+        <v>14.3</v>
       </c>
       <c r="H56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="J56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="M56" s="4" t="n">
-        <v>14.2</v>
+        <v>17.6</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>14.1</v>
+        <v>17.7</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>14.1</v>
+        <v>17.7</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         </is>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>1009</v>
+        <v>1001.7</v>
       </c>
       <c r="R56" s="4" t="n">
         <v>0</v>
@@ -7347,22 +7347,22 @@
         </is>
       </c>
       <c r="Z56" s="4" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.016</v>
       </c>
       <c r="AA56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="AC56" s="5" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AE56" s="5" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF56" s="5" t="n">
         <v>5</v>
@@ -7377,7 +7377,7 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -7386,47 +7386,47 @@
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>14.1</v>
+        <v>17.7</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>14.2</v>
+        <v>17.7</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>13.9</v>
+        <v>17.6</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>11.2</v>
+        <v>14.4</v>
       </c>
       <c r="H57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="J57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M57" s="7" t="n">
-        <v>14.1</v>
+        <v>17.7</v>
       </c>
       <c r="N57" s="7" t="n">
-        <v>13.9</v>
+        <v>17.9</v>
       </c>
       <c r="O57" s="7" t="n">
-        <v>13.9</v>
+        <v>17.9</v>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="Q57" s="7" t="n">
-        <v>1008.9</v>
+        <v>1001.4</v>
       </c>
       <c r="R57" s="7" t="n">
         <v>0</v>
@@ -7473,16 +7473,16 @@
         </is>
       </c>
       <c r="Z57" s="7" t="n">
-        <v>0.089</v>
+        <v>0.014</v>
       </c>
       <c r="AA57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB57" s="7" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="AC57" s="8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD57" s="7" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -7512,47 +7512,47 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>14.1</v>
+        <v>17.6</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>14.1</v>
+        <v>17.7</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>14</v>
+        <v>17.6</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>11.2</v>
+        <v>14.3</v>
       </c>
       <c r="H58" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="J58" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="M58" s="4" t="n">
-        <v>14.1</v>
+        <v>17.6</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>13.9</v>
+        <v>17.7</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>13.9</v>
+        <v>17.7</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>1008.8</v>
+        <v>1001.2</v>
       </c>
       <c r="R58" s="4" t="n">
         <v>0</v>
@@ -7599,16 +7599,16 @@
         </is>
       </c>
       <c r="Z58" s="4" t="n">
-        <v>0.089</v>
+        <v>0.016</v>
       </c>
       <c r="AA58" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB58" s="4" t="n">
-        <v>23</v>
+        <v>24.4</v>
       </c>
       <c r="AC58" s="5" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD58" s="4" t="n">
         <v>0</v>
@@ -7629,7 +7629,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -7638,47 +7638,47 @@
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>14</v>
+        <v>17.2</v>
       </c>
       <c r="D59" s="7" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="G59" s="7" t="n">
         <v>14.1</v>
       </c>
-      <c r="E59" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="F59" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="G59" s="7" t="n">
-        <v>11.2</v>
-      </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="J59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>WNW</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="M59" s="7" t="n">
-        <v>14</v>
+        <v>17.2</v>
       </c>
       <c r="N59" s="7" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="O59" s="7" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="Q59" s="7" t="n">
-        <v>1008.3</v>
+        <v>1001.2</v>
       </c>
       <c r="R59" s="7" t="n">
         <v>0</v>
@@ -7725,16 +7725,16 @@
         </is>
       </c>
       <c r="Z59" s="7" t="n">
-        <v>0.09</v>
+        <v>0.023</v>
       </c>
       <c r="AA59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB59" s="7" t="n">
-        <v>22.9</v>
+        <v>24.3</v>
       </c>
       <c r="AC59" s="8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD59" s="7" t="n">
         <v>0</v>
@@ -7755,7 +7755,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -7764,26 +7764,26 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>13.9</v>
+        <v>17.1</v>
       </c>
       <c r="D60" s="4" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="G60" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E60" s="4" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>11.3</v>
-      </c>
       <c r="H60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="J60" s="4" t="n">
@@ -7794,17 +7794,17 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>13.9</v>
+        <v>17.1</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>13.8</v>
+        <v>17.3</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>13.8</v>
+        <v>17.3</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>1008.1</v>
+        <v>1001.2</v>
       </c>
       <c r="R60" s="4" t="n">
         <v>0</v>
@@ -7851,22 +7851,22 @@
         </is>
       </c>
       <c r="Z60" s="4" t="n">
-        <v>0.091</v>
+        <v>0.025</v>
       </c>
       <c r="AA60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>22.9</v>
+        <v>24.3</v>
       </c>
       <c r="AC60" s="5" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AE60" s="5" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF60" s="5" t="n">
         <v>5</v>
@@ -7881,7 +7881,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -7890,26 +7890,26 @@
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>14.6</v>
+        <v>16.2</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>14.6</v>
+        <v>17.1</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>13.9</v>
+        <v>16.2</v>
       </c>
       <c r="F61" s="8" t="n">
         <v>83</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>11.7</v>
+        <v>13.3</v>
       </c>
       <c r="H61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="J61" s="7" t="n">
@@ -7920,17 +7920,17 @@
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>NNW</t>
         </is>
       </c>
       <c r="M61" s="7" t="n">
-        <v>14.6</v>
+        <v>16.2</v>
       </c>
       <c r="N61" s="7" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
       <c r="O61" s="7" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="Q61" s="7" t="n">
-        <v>1007.9</v>
+        <v>1001.4</v>
       </c>
       <c r="R61" s="7" t="n">
         <v>0</v>
@@ -7977,22 +7977,22 @@
         </is>
       </c>
       <c r="Z61" s="7" t="n">
-        <v>0.079</v>
+        <v>0.044</v>
       </c>
       <c r="AA61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB61" s="7" t="n">
-        <v>22.9</v>
+        <v>24.2</v>
       </c>
       <c r="AC61" s="8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AE61" s="8" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AF61" s="8" t="n">
         <v>5</v>
@@ -8007,7 +8007,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -8016,19 +8016,19 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>15.1</v>
+        <v>16.2</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>14.6</v>
+        <v>14.9</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="H62" s="4" t="n">
         <v>0</v>
@@ -8050,13 +8050,13 @@
         </is>
       </c>
       <c r="M62" s="4" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>1007.8</v>
+        <v>1001.6</v>
       </c>
       <c r="R62" s="4" t="n">
         <v>0</v>
@@ -8103,16 +8103,16 @@
         </is>
       </c>
       <c r="Z62" s="4" t="n">
-        <v>0.067</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AA62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB62" s="4" t="n">
-        <v>22.8</v>
+        <v>24.2</v>
       </c>
       <c r="AC62" s="5" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD62" s="4" t="n">
         <v>0</v>
@@ -8133,7 +8133,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -8142,47 +8142,47 @@
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>16.4</v>
+        <v>14.2</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>16.4</v>
+        <v>14.8</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>15.1</v>
+        <v>14.2</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="H63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>NNE</t>
+          <t>---</t>
         </is>
       </c>
       <c r="J63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>NNE</t>
+          <t>---</t>
         </is>
       </c>
       <c r="M63" s="7" t="n">
-        <v>16.4</v>
+        <v>14.2</v>
       </c>
       <c r="N63" s="7" t="n">
-        <v>16.4</v>
+        <v>14.2</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>16.4</v>
+        <v>14.2</v>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="Q63" s="7" t="n">
-        <v>1008.2</v>
+        <v>1002</v>
       </c>
       <c r="R63" s="7" t="n">
         <v>0</v>
@@ -8229,22 +8229,22 @@
         </is>
       </c>
       <c r="Z63" s="7" t="n">
-        <v>0.039</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AA63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB63" s="7" t="n">
-        <v>22.8</v>
+        <v>24.1</v>
       </c>
       <c r="AC63" s="8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AE63" s="8" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AF63" s="8" t="n">
         <v>5</v>
@@ -8259,7 +8259,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -8268,26 +8268,26 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>15.3</v>
+        <v>13.8</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>16.6</v>
+        <v>14.2</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>15.3</v>
+        <v>13.8</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="H64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>WNW</t>
         </is>
       </c>
       <c r="J64" s="4" t="n">
@@ -8298,17 +8298,17 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>WNW</t>
         </is>
       </c>
       <c r="M64" s="4" t="n">
-        <v>15.3</v>
+        <v>13.8</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>1008.2</v>
+        <v>1002.5</v>
       </c>
       <c r="R64" s="4" t="n">
         <v>0</v>
@@ -8355,16 +8355,16 @@
         </is>
       </c>
       <c r="Z64" s="4" t="n">
-        <v>0.064</v>
+        <v>0.094</v>
       </c>
       <c r="AA64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>22.8</v>
+        <v>24.1</v>
       </c>
       <c r="AC64" s="5" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AD64" s="4" t="n">
         <v>0</v>
@@ -8385,7 +8385,7 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -8394,47 +8394,47 @@
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>14.7</v>
+        <v>13.5</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>15.3</v>
+        <v>13.8</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>14.7</v>
+        <v>13.5</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="H65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="J65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>---</t>
         </is>
       </c>
       <c r="M65" s="7" t="n">
-        <v>14.7</v>
+        <v>13.5</v>
       </c>
       <c r="N65" s="7" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="O65" s="7" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="Q65" s="7" t="n">
-        <v>1008.3</v>
+        <v>1003.2</v>
       </c>
       <c r="R65" s="7" t="n">
         <v>0</v>
@@ -8481,22 +8481,22 @@
         </is>
       </c>
       <c r="Z65" s="7" t="n">
-        <v>0.076</v>
+        <v>0.101</v>
       </c>
       <c r="AA65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB65" s="7" t="n">
-        <v>22.7</v>
+        <v>24</v>
       </c>
       <c r="AC65" s="8" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AD65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AE65" s="8" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AF65" s="8" t="n">
         <v>5</v>
@@ -8511,7 +8511,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -8520,47 +8520,47 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>15.4</v>
+        <v>13.2</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>15.4</v>
+        <v>13.5</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="H66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>WNW</t>
         </is>
       </c>
       <c r="J66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>WNW</t>
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>15.4</v>
+        <v>13.2</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>15.4</v>
+        <v>13.3</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>15.4</v>
+        <v>13.3</v>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>1008.6</v>
+        <v>1003.8</v>
       </c>
       <c r="R66" s="4" t="n">
         <v>0</v>
@@ -8607,22 +8607,22 @@
         </is>
       </c>
       <c r="Z66" s="4" t="n">
-        <v>0.06</v>
+        <v>0.106</v>
       </c>
       <c r="AA66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>22.7</v>
+        <v>23.9</v>
       </c>
       <c r="AC66" s="5" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AD66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AE66" s="5" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AF66" s="5" t="n">
         <v>5</v>
@@ -8637,7 +8637,7 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -8646,19 +8646,19 @@
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>16.7</v>
+        <v>14.2</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>16.7</v>
+        <v>14.2</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>15.5</v>
+        <v>13.2</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
@@ -8680,13 +8680,13 @@
         </is>
       </c>
       <c r="M67" s="7" t="n">
-        <v>16.7</v>
+        <v>14.2</v>
       </c>
       <c r="N67" s="7" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="Q67" s="7" t="n">
-        <v>1009</v>
+        <v>1004.7</v>
       </c>
       <c r="R67" s="7" t="n">
         <v>0</v>
@@ -8733,16 +8733,16 @@
         </is>
       </c>
       <c r="Z67" s="7" t="n">
-        <v>0.034</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AA67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB67" s="7" t="n">
-        <v>22.6</v>
+        <v>23.8</v>
       </c>
       <c r="AC67" s="8" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="AD67" s="7" t="n">
         <v>0</v>
@@ -8763,7 +8763,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -8772,47 +8772,47 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>16.7</v>
+        <v>14.2</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="H68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ESE</t>
         </is>
       </c>
       <c r="J68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ESE</t>
         </is>
       </c>
       <c r="M68" s="4" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>17.6</v>
+        <v>15.8</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>17.6</v>
+        <v>15.8</v>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>1009.3</v>
+        <v>1005.7</v>
       </c>
       <c r="R68" s="4" t="n">
         <v>0</v>
@@ -8859,16 +8859,16 @@
         </is>
       </c>
       <c r="Z68" s="4" t="n">
-        <v>0.016</v>
+        <v>0.057</v>
       </c>
       <c r="AA68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
       <c r="AC68" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AD68" s="4" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>11/09/26</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -8898,26 +8898,26 @@
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>18.9</v>
+        <v>17.3</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>18.9</v>
+        <v>17.3</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>13.9</v>
+        <v>14.5</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J69" s="7" t="n">
@@ -8928,17 +8928,17 @@
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>E</t>
         </is>
       </c>
       <c r="M69" s="7" t="n">
-        <v>18.9</v>
+        <v>17.3</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>18.9</v>
+        <v>17.5</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>18.9</v>
+        <v>17.5</v>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="Q69" s="7" t="n">
-        <v>1009.2</v>
+        <v>1006.1</v>
       </c>
       <c r="R69" s="7" t="n">
         <v>0</v>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="Z69" s="7" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="AA69" s="7" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AB69" s="7" t="n">
-        <v>22.9</v>
+        <v>24.1</v>
       </c>
       <c r="AC69" s="8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AD69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AE69" s="8" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AF69" s="8" t="n">
         <v>5</v>
@@ -9009,1392 +9009,6 @@
         <v>100</v>
       </c>
       <c r="AH69" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>10/09/26</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>9:30</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="O70" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="P70" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Q70" s="4" t="n">
-        <v>1009</v>
-      </c>
-      <c r="R70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="U70" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="V70" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="W70" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="X70" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Y70" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Z70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA70" s="4" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="AB70" s="4" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="AC70" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="AD70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE70" s="5" t="n">
-        <v>640</v>
-      </c>
-      <c r="AF70" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG70" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH70" s="5" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>10/09/26</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="D71" s="7" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="E71" s="7" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F71" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="G71" s="7" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="H71" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L71" s="6" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="M71" s="7" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="N71" s="7" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="O71" s="7" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="P71" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Q71" s="7" t="n">
-        <v>1008.9</v>
-      </c>
-      <c r="R71" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="U71" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="V71" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="W71" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="X71" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Y71" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Z71" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA71" s="7" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="AB71" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC71" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="AD71" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE71" s="8" t="n">
-        <v>640</v>
-      </c>
-      <c r="AF71" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG71" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH71" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>10/09/26</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="E72" s="4" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="G72" s="4" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="H72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L72" s="3" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="M72" s="4" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N72" s="4" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="O72" s="4" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="P72" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Q72" s="4" t="n">
-        <v>1008.7</v>
-      </c>
-      <c r="R72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="U72" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="V72" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="W72" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="X72" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Y72" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Z72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA72" s="4" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="AB72" s="4" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="AC72" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="AD72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE72" s="5" t="n">
-        <v>639</v>
-      </c>
-      <c r="AF72" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG72" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH72" s="5" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>10/09/26</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="D73" s="7" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E73" s="7" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="F73" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="G73" s="7" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="H73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="J73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L73" s="6" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="M73" s="7" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="N73" s="7" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="O73" s="7" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="P73" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Q73" s="7" t="n">
-        <v>1008.5</v>
-      </c>
-      <c r="R73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="U73" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="V73" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="W73" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="X73" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Y73" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Z73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA73" s="7" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="AB73" s="7" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="AC73" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="AD73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE73" s="8" t="n">
-        <v>640</v>
-      </c>
-      <c r="AF73" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG73" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH73" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>10/09/26</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="G74" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="M74" s="4" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="N74" s="4" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="O74" s="4" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="P74" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Q74" s="4" t="n">
-        <v>1008.1</v>
-      </c>
-      <c r="R74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="U74" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="V74" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="W74" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="X74" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Y74" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Z74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA74" s="4" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="AB74" s="4" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AC74" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="AD74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE74" s="5" t="n">
-        <v>639</v>
-      </c>
-      <c r="AF74" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG74" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH74" s="5" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>10/09/26</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="D75" s="7" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E75" s="7" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="F75" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="G75" s="7" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="H75" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="L75" s="6" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="M75" s="7" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="N75" s="7" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="O75" s="7" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="P75" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Q75" s="7" t="n">
-        <v>1007.2</v>
-      </c>
-      <c r="R75" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="U75" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="V75" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="W75" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="X75" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Y75" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Z75" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA75" s="7" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="AB75" s="7" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AC75" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="AD75" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE75" s="8" t="n">
-        <v>639</v>
-      </c>
-      <c r="AF75" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG75" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH75" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>10/09/26</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="J76" s="4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="K76" s="4" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="L76" s="3" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="M76" s="4" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="N76" s="4" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="O76" s="4" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="P76" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Q76" s="4" t="n">
-        <v>1006.3</v>
-      </c>
-      <c r="R76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="U76" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="V76" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="W76" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="X76" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Y76" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Z76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="4" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="AB76" s="4" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AC76" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="AD76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE76" s="5" t="n">
-        <v>640</v>
-      </c>
-      <c r="AF76" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG76" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH76" s="5" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>10/09/26</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="D77" s="7" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="E77" s="7" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="F77" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="G77" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="H77" s="7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="J77" s="7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="K77" s="7" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="L77" s="6" t="inlineStr">
-        <is>
-          <t>ENE</t>
-        </is>
-      </c>
-      <c r="M77" s="7" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="N77" s="7" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="O77" s="7" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="P77" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Q77" s="7" t="n">
-        <v>1005.2</v>
-      </c>
-      <c r="R77" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="U77" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="V77" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="W77" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="X77" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Y77" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Z77" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA77" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AB77" s="7" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="AC77" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="AD77" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE77" s="8" t="n">
-        <v>640</v>
-      </c>
-      <c r="AF77" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG77" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH77" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>10/09/26</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>NE</t>
-        </is>
-      </c>
-      <c r="J78" s="4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="K78" s="4" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="L78" s="3" t="inlineStr">
-        <is>
-          <t>ENE</t>
-        </is>
-      </c>
-      <c r="M78" s="4" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="N78" s="4" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="O78" s="4" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="P78" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Q78" s="4" t="n">
-        <v>1004.1</v>
-      </c>
-      <c r="R78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="U78" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="V78" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="W78" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="X78" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Y78" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Z78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="4" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="AB78" s="4" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="AC78" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="AD78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE78" s="5" t="n">
-        <v>640</v>
-      </c>
-      <c r="AF78" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG78" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH78" s="5" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>10/09/26</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="D79" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="E79" s="7" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="F79" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="G79" s="7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="H79" s="7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>NE</t>
-        </is>
-      </c>
-      <c r="J79" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K79" s="7" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="L79" s="6" t="inlineStr">
-        <is>
-          <t>NE</t>
-        </is>
-      </c>
-      <c r="M79" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="N79" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="O79" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="P79" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Q79" s="7" t="n">
-        <v>1003.1</v>
-      </c>
-      <c r="R79" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="U79" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="V79" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="W79" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="X79" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Y79" s="6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Z79" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA79" s="7" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AB79" s="7" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="AC79" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="AD79" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE79" s="8" t="n">
-        <v>640</v>
-      </c>
-      <c r="AF79" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG79" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH79" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>10/09/26</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="G80" s="4" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="H80" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>NE</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="K80" s="4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="L80" s="3" t="inlineStr">
-        <is>
-          <t>NE</t>
-        </is>
-      </c>
-      <c r="M80" s="4" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="N80" s="4" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="O80" s="4" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="P80" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Q80" s="4" t="n">
-        <v>1002.5</v>
-      </c>
-      <c r="R80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="U80" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="V80" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="W80" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="X80" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Y80" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Z80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="4" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="AB80" s="4" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AC80" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="AD80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE80" s="5" t="n">
-        <v>640</v>
-      </c>
-      <c r="AF80" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG80" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH80" s="5" t="n">
         <v>30</v>
       </c>
     </row>

--- a/downld02.xlsx
+++ b/downld02.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH69"/>
+  <dimension ref="A1:AH72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9012,6 +9012,384 @@
         <v>30</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>11/09/26</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>9:30</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q70" s="4" t="n">
+        <v>1006.4</v>
+      </c>
+      <c r="R70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U70" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V70" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W70" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X70" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y70" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="AB70" s="4" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AC70" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF70" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG70" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH70" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>11/09/26</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G71" s="7" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H71" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K71" s="7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="M71" s="7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="N71" s="7" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="O71" s="7" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="n">
+        <v>1007</v>
+      </c>
+      <c r="R71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U71" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V71" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W71" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X71" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y71" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="7" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="AB71" s="7" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AC71" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF71" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG71" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH71" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>11/09/26</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="O72" s="4" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="n">
+        <v>1007.8</v>
+      </c>
+      <c r="R72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U72" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V72" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W72" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y72" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="4" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AB72" s="4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AC72" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF72" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH72" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AH1"/>

--- a/downld02.xlsx
+++ b/downld02.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH72"/>
+  <dimension ref="A1:AH75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9390,6 +9390,384 @@
         <v>30</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>11/09/26</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L73" s="6" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="M73" s="7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="N73" s="7" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="O73" s="7" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q73" s="7" t="n">
+        <v>1008.1</v>
+      </c>
+      <c r="R73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U73" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V73" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W73" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X73" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y73" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="7" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AB73" s="7" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AC73" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="AD73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF73" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG73" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH73" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>11/09/26</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="O74" s="4" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="n">
+        <v>1008.2</v>
+      </c>
+      <c r="R74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U74" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V74" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W74" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X74" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y74" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="4" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AB74" s="4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AC74" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF74" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG74" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH74" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>11/09/26</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L75" s="6" t="inlineStr">
+        <is>
+          <t>WSW</t>
+        </is>
+      </c>
+      <c r="M75" s="7" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="N75" s="7" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="O75" s="7" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q75" s="7" t="n">
+        <v>1007.9</v>
+      </c>
+      <c r="R75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U75" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V75" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W75" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X75" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y75" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="7" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AB75" s="7" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AC75" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="AD75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF75" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG75" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH75" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AH1"/>
